--- a/diseases/d167/2000-2004.xlsx
+++ b/diseases/d167/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">

--- a/diseases/d167/2000-2004.xlsx
+++ b/diseases/d167/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">

--- a/diseases/d167/2000-2004.xlsx
+++ b/diseases/d167/2000-2004.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.005045547545216242</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>1</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.005045547545216242</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.005045547545216242</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.005045547545216242</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>3</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.01513664263564873</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>4</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.02018219018086497</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.005045547545216242</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.005045547545216242</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>2</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.009976715841732773</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>2</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.009976715841732773</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>1</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.004988357920866386</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.004988357920866386</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.004988357920866386</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.004988357920866386</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.004988357920866386</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>1</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.004988357920866386</v>
       </c>
@@ -24128,9 +23951,6 @@
       </c>
       <c r="O120" t="n">
         <v>1</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0.004988357920866386</v>

--- a/diseases/d167/2000-2004.xlsx
+++ b/diseases/d167/2000-2004.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20661,7 +20661,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23805,7 +23805,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">

--- a/diseases/d167/2000-2004.xlsx
+++ b/diseases/d167/2000-2004.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">

--- a/diseases/d167/2000-2004.xlsx
+++ b/diseases/d167/2000-2004.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">

--- a/diseases/d167/2000-2004.xlsx
+++ b/diseases/d167/2000-2004.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19978,12 +19978,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -20008,22 +20008,22 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>0.01949042384314224</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -20032,12 +20032,12 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_CZ_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -20057,7 +20057,7 @@
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_CZ_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT100" t="n">
@@ -20070,42 +20070,42 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -20137,12 +20137,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -20167,38 +20167,38 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_CZ_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_CZ_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_CZ_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>Syphilis congenital</t>
+          <t>Syphilis, congenital</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
@@ -20208,12 +20208,12 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:CZ:national</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG101" t="inlineStr">
@@ -20258,17 +20258,17 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
+          <t>Czechia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_CZ_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -20304,42 +20304,42 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -20371,12 +20371,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -20401,22 +20401,22 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>0.0115648206113599</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -20425,12 +20425,12 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_ES_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -20450,7 +20450,7 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_ES_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -20463,42 +20463,42 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -20530,12 +20530,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -20560,38 +20560,38 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_ES_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_ES_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_ES_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>Syphilis congenital</t>
+          <t>Syphilis, congenital</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -20601,12 +20601,12 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
@@ -20616,7 +20616,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:ES:national</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
@@ -20631,7 +20631,7 @@
       </c>
       <c r="AF103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG103" t="inlineStr">
@@ -20651,17 +20651,17 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -20684,7 +20684,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_ES_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT103" t="n">
@@ -20697,42 +20697,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -20764,12 +20764,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -20794,22 +20794,22 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O104" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R104" t="n">
-        <v>0.009976715841732773</v>
+        <v>0.01031340060965089</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20818,12 +20818,12 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_IT_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -20843,7 +20843,7 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_IT_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT104" t="n">
@@ -20856,42 +20856,42 @@
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -20923,12 +20923,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -20953,38 +20953,38 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_IT_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_IT_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_IT_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>Syphilis congenital</t>
+          <t>Syphilis, congenital</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -20994,12 +20994,12 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
@@ -21009,7 +21009,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:IT:national</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="AF105" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG105" t="inlineStr">
@@ -21044,17 +21044,17 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
+          <t>Italy annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21077,7 +21077,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_IT_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT105" t="n">
@@ -21090,42 +21090,42 @@
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -21157,12 +21157,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -21187,22 +21187,22 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O106" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R106" t="n">
-        <v>0.004988357920866386</v>
+        <v>0.1240294516519602</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -21211,12 +21211,12 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_PT_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_PT_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -21249,42 +21249,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -21316,12 +21316,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -21346,38 +21346,38 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O107" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_PT_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_PT_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_PT_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>Syphilis congenital</t>
+          <t>Syphilis, congenital</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -21387,12 +21387,12 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:PT:national</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -21417,7 +21417,7 @@
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
@@ -21437,17 +21437,17 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
+          <t>Portugal annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21470,7 +21470,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_PT_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -21483,42 +21483,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -21550,12 +21550,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -21580,22 +21580,22 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="O108" t="n">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="R108" t="n">
-        <v>0.004988357920866386</v>
+        <v>0.6354184832257113</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -21604,12 +21604,12 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_RO_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -21629,7 +21629,7 @@
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_RO_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT108" t="n">
@@ -21642,42 +21642,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -21709,12 +21709,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -21739,38 +21739,38 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="O109" t="n">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_RO_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_RO_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_RO_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>Syphilis congenital</t>
+          <t>Syphilis, congenital</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -21780,12 +21780,12 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
@@ -21795,7 +21795,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:RO:national</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr">
@@ -21810,7 +21810,7 @@
       </c>
       <c r="AF109" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG109" t="inlineStr">
@@ -21830,17 +21830,17 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
+          <t>Romania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_RO_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT109" t="n">
@@ -21876,42 +21876,42 @@
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -21973,22 +21973,22 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>0.004988357920866386</v>
+        <v>0</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -22132,19 +22132,19 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22366,12 +22366,12 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N112" t="n">
@@ -22525,12 +22525,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N113" t="n">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22759,22 +22759,22 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R114" t="n">
-        <v>0.004988357920866386</v>
+        <v>0.009976715841732773</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -22918,19 +22918,19 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23152,12 +23152,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N116" t="n">
@@ -23311,12 +23311,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N117" t="n">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23545,12 +23545,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N118" t="n">
@@ -23704,12 +23704,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N119" t="n">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23938,12 +23938,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N120" t="n">
@@ -24097,12 +24097,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N121" t="n">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24268,6 +24268,1971 @@
         </is>
       </c>
       <c r="BC121" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2004-08-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2004-08</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2004-08-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2004-08</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2004-09</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" t="n">
+        <v>1</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.004988357920866386</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2004-09</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2004-10</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.004988357920866386</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2004-10</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>1</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.004988357920866386</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.004988357920866386</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -24389,7 +26354,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -24399,7 +26364,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -24419,7 +26384,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -24429,7 +26394,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -24451,7 +26416,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16">
